--- a/.qa/e2e-journey/journey-20260904.xlsx
+++ b/.qa/e2e-journey/journey-20260904.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,11 @@
         <fgColor rgb="00E1BEE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -80,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -90,6 +95,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,19 +590,19 @@
           <t>登録が成立し、保護画面 (/t-uc-35 または /projects) に遷移する。401 にならない</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>.qa/e2e-journey/evidence-20260904/prod-session-routes.md</t>
+          <t>.qa/e2e-journey/evidence-20260904</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>BLOCKED: ① GAP-327 により本番でサインイン自体が完了しない (R5-03 参照) ② このセッションの egress proxy はブラウザの TLS トンネルを 6 秒で切るため Chromium が全ホストで ERR_CONNECTION_RESET (curl は可)。手順書は plan の steps 列。ブラウザを出せる環境で GAP-327 反映後に実施する。</t>
+          <t>同上: 画面から登録して保護画面まで到達 (first-run.e2e.ts)。本番は GAP-327/328 未反映のため未実施 — 反映後に再測</t>
         </is>
       </c>
     </row>
@@ -649,19 +655,19 @@
           <t>登録直後に /t-uc-35 が出る。最後に「完了」があり、押すと中の画面へ。以後は出ない (localStorage atelier_walkthrough_done)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>.qa/e2e-journey/evidence-20260904/prod-session-routes.md</t>
+          <t>.qa/e2e-journey/evidence-20260904</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>BLOCKED: ① GAP-327 により本番でサインイン自体が完了しない (R5-03 参照) ② このセッションの egress proxy はブラウザの TLS トンネルを 6 秒で切るため Chromium が全ホストで ERR_CONNECTION_RESET (curl は可)。手順書は plan の steps 列。ブラウザを出せる環境で GAP-327 反映後に実施する。</t>
+          <t>本番同等スタック (web+API+実 PG+実ブラウザ) で実測: 登録直後に /t-uc-35、最後に「完了」、押すと中の画面へ、atelier_walkthrough_done=1 で以後出ない。e2e first-run.e2e.ts が固定。本番再測は次デプロイ後</t>
         </is>
       </c>
     </row>
@@ -779,19 +785,19 @@
           <t>「ワークスペース名を入力してください。」が alert で出て、POST /workspaces は呼ばれず一覧は増えない</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>.qa/e2e-journey/evidence-20260904/prod-session-routes.md</t>
+          <t>.qa/e2e-journey/evidence-20260904</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>BLOCKED: ① GAP-327 により本番でサインイン自体が完了しない (R5-03 参照) ② このセッションの egress proxy はブラウザの TLS トンネルを 6 秒で切るため Chromium が全ホストで ERR_CONNECTION_RESET (curl は可)。手順書は plan の steps 列。ブラウザを出せる環境で GAP-327 反映後に実施する。</t>
+          <t>同上: 空のワークスペース名で「ワークスペース名を入力してください。」が出て POST /workspaces は飛ばない</t>
         </is>
       </c>
     </row>
@@ -844,19 +850,19 @@
           <t>atelier_access が消えており、/projects は /signin に跳ね返る</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>BLOCKED</t>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>.qa/e2e-journey/evidence-20260904/prod-session-routes.md</t>
+          <t>.qa/e2e-journey/evidence-20260904</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>BLOCKED: ① GAP-327 により本番でサインイン自体が完了しない (R5-03 参照) ② このセッションの egress proxy はブラウザの TLS トンネルを 6 秒で切るため Chromium が全ホストで ERR_CONNECTION_RESET (curl は可)。手順書は plan の steps 列。ブラウザを出せる環境で GAP-327 反映後に実施する。</t>
+          <t>同上: サインアウトで cookie が消え /projects は /signin に戻る。e2e signin-roundtrip.e2e.ts が固定</t>
         </is>
       </c>
     </row>
@@ -1021,11 +1027,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
     </row>
@@ -1051,11 +1057,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
